--- a/jira_export_2026-09-24.xlsx
+++ b/jira_export_2026-09-24.xlsx
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>365 h</t>
+          <t>373 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -4096,7 +4096,7 @@
         <v>3</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>1452.5</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>161.39</v>
+        <v>132.05</v>
       </c>
     </row>
     <row r="48">
@@ -4553,11 +4553,7 @@
           <t>[SETE] - AME LiEx</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+      <c r="C54" s="14" t="inlineStr"/>
       <c r="D54" s="14" t="inlineStr">
         <is>
           <t>COMMUNE DE SETE</t>
@@ -4664,7 +4660,7 @@
         <v>3</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
@@ -4683,7 +4679,7 @@
         <v>355</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>0</v>
+        <v>118.33</v>
       </c>
     </row>
     <row r="56">
@@ -8832,7 +8828,7 @@
         <v>8</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
@@ -11142,7 +11138,7 @@
         <v>17</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="L146" s="14" t="inlineStr">
         <is>
@@ -11764,7 +11760,7 @@
         <v>21</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>24.33</v>
+        <v>24.83</v>
       </c>
       <c r="L155" s="11" t="inlineStr"/>
       <c r="M155" s="11" t="inlineStr"/>
@@ -13219,7 +13215,7 @@
         <v>47071.25800000001</v>
       </c>
       <c r="P179" s="18" t="n">
-        <v>194.24</v>
+        <v>188.6</v>
       </c>
     </row>
   </sheetData>
@@ -13410,7 +13406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -13436,7 +13432,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 10 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 12 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -13607,22 +13603,22 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35000</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PALAVAS-LES-FLOTS] - Ajout d'un Pax + Carte M2M + reinst apk et cb</t>
+          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Pax + Carte M2M + reinst apk et cb</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -13637,7 +13633,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H7" s="11" t="n">
@@ -13645,12 +13641,12 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35006</t>
+          <t>PDMDEP-35112</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>00178435</t>
+          <t>00178807</t>
         </is>
       </c>
       <c r="K7" s="12" t="n">
@@ -13660,22 +13656,22 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[COMMUNE DE PALAVAS-LES-FLOTS] - Ajout d'un Pax + Carte M2M + reinst apk et cb</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Ajout d'un Pax + Carte M2M + reinst apk et cb</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -13690,7 +13686,7 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H8" s="14" t="n">
@@ -13698,12 +13694,12 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34789</t>
+          <t>PDMDEP-35006</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>00177123</t>
+          <t>00178435</t>
         </is>
       </c>
       <c r="K8" s="15" t="n">
@@ -13713,22 +13709,22 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -13751,12 +13747,12 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34638</t>
+          <t>PDMDEP-34789</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>00176478</t>
+          <t>00177123</t>
         </is>
       </c>
       <c r="K9" s="12" t="n">
@@ -13766,22 +13762,22 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34613</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE FORT-DE-FRANCE] - Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE FORT-DE-FRANCE</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -13796,7 +13792,7 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="H10" s="14" t="n">
@@ -13804,37 +13800,37 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34619</t>
+          <t>PDMDEP-34638</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>00176429</t>
+          <t>00176478</t>
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>3260</v>
+        <v>815</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34613</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
+          <t>[COMMUNE DE FORT-DE-FRANCE] - Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE FORT-DE-FRANCE</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER simple</t>
+          <t>Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -13849,7 +13845,7 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H11" s="11" t="n">
@@ -13857,37 +13853,37 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34587</t>
+          <t>PDMDEP-34619</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>00176129</t>
+          <t>00176429</t>
         </is>
       </c>
       <c r="K11" s="12" t="n">
-        <v>815</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>MIGRATION GEODP PLACIER simple</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -13902,7 +13898,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H12" s="14" t="n">
@@ -13910,12 +13906,12 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33507</t>
+          <t>PDMDEP-34587</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>00168118</t>
+          <t>00176129</t>
         </is>
       </c>
       <c r="K12" s="15" t="n">
@@ -13925,22 +13921,22 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -13963,12 +13959,12 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33019</t>
+          <t>PDMDEP-34088</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>00165370</t>
+          <t>00170725</t>
         </is>
       </c>
       <c r="K13" s="12" t="n">
@@ -13978,22 +13974,22 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32950</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 1/2</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -14008,7 +14004,7 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="H14" s="14" t="n">
@@ -14016,12 +14012,12 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32956</t>
+          <t>PDMDEP-33507</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>00165250</t>
+          <t>00168118</t>
         </is>
       </c>
       <c r="K14" s="15" t="n">
@@ -14029,22 +14025,128 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-33012</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE GRASSE</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33019</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>00165370</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-32950</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DU PONTET</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Migration GeODP Placier 1/2</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32956</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>00165250</t>
+        </is>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr"/>
-      <c r="C15" s="17" t="inlineStr"/>
-      <c r="D15" s="17" t="inlineStr"/>
-      <c r="E15" s="17" t="inlineStr"/>
-      <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr"/>
-      <c r="H15" s="17" t="inlineStr"/>
-      <c r="I15" s="17" t="inlineStr"/>
-      <c r="J15" s="17" t="inlineStr"/>
-      <c r="K15" s="18" t="n">
-        <v>10595</v>
+      <c r="B17" s="17" t="inlineStr"/>
+      <c r="C17" s="17" t="inlineStr"/>
+      <c r="D17" s="17" t="inlineStr"/>
+      <c r="E17" s="17" t="inlineStr"/>
+      <c r="F17" s="17" t="inlineStr"/>
+      <c r="G17" s="17" t="inlineStr"/>
+      <c r="H17" s="17" t="inlineStr"/>
+      <c r="I17" s="17" t="inlineStr"/>
+      <c r="J17" s="17" t="inlineStr"/>
+      <c r="K17" s="18" t="n">
+        <v>12225</v>
       </c>
     </row>
   </sheetData>
@@ -14060,6 +14162,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14534,16 +14638,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>126.42</v>
+        <v>128.17</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>44.42</v>
+        <v>44.92</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>16.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>187.08</v>
+        <v>189.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>24.17</v>
@@ -14553,7 +14657,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.2%</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14668,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -14573,7 +14677,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>53.5</v>
+        <v>58.5</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>5.5</v>
@@ -14583,7 +14687,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14699,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>91.25</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -14683,13 +14787,13 @@
         <v>405525</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>168977</v>
+        <v>162210</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>236548</v>
+        <v>243314</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>143335</v>
+        <v>150102</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>25787</v>
@@ -14708,13 +14812,13 @@
         <v>178989</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>67786</v>
+        <v>61019</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>111203</v>
+        <v>117970</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>95659</v>
+        <v>102425</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>

--- a/jira_export_2026-09-24.xlsx
+++ b/jira_export_2026-09-24.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>48,441 €</t>
+          <t>49,079 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -763,7 +763,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>11,866 €</t>
+          <t>12,504 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -1399,11 +1399,11 @@
       <c r="N9" s="12" t="n">
         <v>600</v>
       </c>
-      <c r="O9" s="16" t="n">
-        <v>0</v>
+      <c r="O9" s="12" t="n">
+        <v>638.25</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>0</v>
+        <v>283.67</v>
       </c>
     </row>
     <row r="10">
@@ -13284,10 +13284,10 @@
         <v>47994.225</v>
       </c>
       <c r="O180" s="18" t="n">
-        <v>48441.108</v>
+        <v>49079.358</v>
       </c>
       <c r="P180" s="18" t="n">
-        <v>191.6</v>
+        <v>194.12</v>
       </c>
     </row>
   </sheetData>
@@ -14857,10 +14857,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>404155</v>
+        <v>403517</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>170057</v>
+        <v>169419</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>234097</v>
@@ -14882,10 +14882,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>178989</v>
+        <v>178351</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>56975</v>
+        <v>56337</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>122014</v>
